--- a/fake_data.xlsx
+++ b/fake_data.xlsx
@@ -419,120 +419,120 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sean Martinez</t>
+          <t>Bryan Beck</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>anthony13@example.org</t>
+          <t>johndavis@example.net</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chelsea Parsons</t>
+          <t>Audrey Henderson</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>jessicasimmons@example.net</t>
+          <t>kristinaowens@example.com</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alyssa Stuart DDS</t>
+          <t>Brian Reynolds</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>danielgraham@example.com</t>
+          <t>margaret50@example.net</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Matthew Fitzgerald</t>
+          <t>Olivia Weber</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>anahubbard@example.net</t>
+          <t>alanlee@example.org</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Rebecca Glenn</t>
+          <t>Claire Christensen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>davisstephen@example.net</t>
+          <t>michaelewing@example.net</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Victoria Smith</t>
+          <t>Dr. Daniel Walsh</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>kelly66@example.com</t>
+          <t>aaron41@example.net</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Amy Hood</t>
+          <t>Christine Brown</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>julieyoung@example.net</t>
+          <t>staffordkatelyn@example.com</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Thomas Gonzalez</t>
+          <t>Kristin Hahn</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>harringtondaniel@example.net</t>
+          <t>beckerjonathan@example.net</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Joseph Jones</t>
+          <t>Cassandra Walker</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>jamie39@example.org</t>
+          <t>lwilliams@example.com</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jason Brown</t>
+          <t>Dan Morales</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dchase@example.org</t>
+          <t>hgarcia@example.net</t>
         </is>
       </c>
     </row>
